--- a/backend/wp_templates/D/D5 应收款项融资.xlsx
+++ b/backend/wp_templates/D/D5 应收款项融资.xlsx
@@ -9100,7 +9100,7 @@
       <c r="M12" s="71"/>
       <c r="N12" s="71"/>
       <c r="O12" s="77">
-        <f>J12+N12+M12</f>
+        <f>L12+M12+N12</f>
         <v>0</v>
       </c>
       <c r="P12" s="78"/>
@@ -9131,7 +9131,7 @@
       <c r="M13" s="71"/>
       <c r="N13" s="71"/>
       <c r="O13" s="77">
-        <f t="shared" ref="O13:O16" si="3">J13+N13+M13</f>
+        <f t="shared" ref="O13:O16" si="3">L13+M13+N13</f>
         <v>0</v>
       </c>
       <c r="P13" s="78"/>
@@ -10020,10 +10020,16 @@
       <c r="D13" s="19"/>
       <c r="E13" s="20"/>
       <c r="F13" s="21"/>
-      <c r="G13" s="22"/>
+      <c r="G13" s="22">
+        <f>F13-E13</f>
+      </c>
       <c r="H13" s="23"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="37"/>
+      <c r="I13" s="19">
+        <f>D13*H13*G13/365</f>
+      </c>
+      <c r="J13" s="37">
+        <f>D13-I13</f>
+      </c>
       <c r="K13" s="37">
         <f t="shared" ref="K13:K16" si="0">J13</f>
         <v>0</v>
@@ -10038,10 +10044,16 @@
       <c r="D14" s="19"/>
       <c r="E14" s="20"/>
       <c r="F14" s="21"/>
-      <c r="G14" s="22"/>
+      <c r="G14" s="22">
+        <f>F14-E14</f>
+      </c>
       <c r="H14" s="23"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="37"/>
+      <c r="I14" s="19">
+        <f>D14*H14*G14/365</f>
+      </c>
+      <c r="J14" s="37">
+        <f>D14-I14</f>
+      </c>
       <c r="K14" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -10056,10 +10068,16 @@
       <c r="D15" s="19"/>
       <c r="E15" s="20"/>
       <c r="F15" s="21"/>
-      <c r="G15" s="22"/>
+      <c r="G15" s="22">
+        <f>F15-E15</f>
+      </c>
       <c r="H15" s="23"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="37"/>
+      <c r="I15" s="19">
+        <f>D15*H15*G15/365</f>
+      </c>
+      <c r="J15" s="37">
+        <f>D15-I15</f>
+      </c>
       <c r="K15" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -10074,10 +10092,16 @@
       <c r="D16" s="19"/>
       <c r="E16" s="20"/>
       <c r="F16" s="21"/>
-      <c r="G16" s="22"/>
+      <c r="G16" s="22">
+        <f>F16-E16</f>
+      </c>
       <c r="H16" s="23"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="37"/>
+      <c r="I16" s="19">
+        <f>D16*H16*G16/365</f>
+      </c>
+      <c r="J16" s="37">
+        <f>D16-I16</f>
+      </c>
       <c r="K16" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
